--- a/70_input/72_Kleingetriebepruefstand_KV3/kst-E_Laufversuche_KV3.xlsx
+++ b/70_input/72_Kleingetriebepruefstand_KV3/kst-E_Laufversuche_KV3.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timkuhn/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub-tkuhn39\semesterthesis\70_input\72_Kleingetriebepruefstand_KV3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75AFBA3-E1E4-4246-A811-F7CAAAB0EFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D51430-287A-45D1-8DC7-9A3CD7F5BD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="1160" windowWidth="27840" windowHeight="16240" xr2:uid="{09DE1DE6-8CB8-D84C-8367-607651AAD6B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{09DE1DE6-8CB8-D84C-8367-607651AAD6B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -470,9 +470,6 @@
     <t>2 034 128</t>
   </si>
   <si>
-    <t>sehr schwankend("ssc"): Stopp nach 2min (2 327), (ab ssc: 13,3…15,7bzw16,0Nm) (auch später: 13,1…15,0Nm) bis 36 349; (ab 13,9Nm…15,7Nm:) 304 112; (ab 13,4…15,8Nm:) 1 019 086; (ab 13,5…15,8Nm:) 1 909 028; (ab 14,0…15,4Nm:) 1 963 654(vorzeitig nachgezogen bei 13,2Nm bei 112 246); (1b 15,0Nm:) 2 797 497; (ab 14,9Nm:) 3 155 930, (ab 14,2Nm:) 3 270 913; (ab 14,3Nm:) 3 302 857, (ab 14,0...15,1:) 2 034 128</t>
-  </si>
-  <si>
     <t>kst-E_34</t>
   </si>
   <si>
@@ -884,13 +881,6 @@
     <t>16,2-16,4</t>
   </si>
   <si>
-    <t>160000 15,2 Nm --&gt; nachverspannt auf 17,2-17,3 Nm, bei 72 °C obwohl steuerung auf 67 eingestellt
-962000 13,7 Nm --&gt; nachverspannt auf  16,5-16,7 Nm, bei 70 °C leichte Ermüdung im Zahnfußbereich zu sehen, aber eher hellere Zahnflächen, was auf Verschleiß hindeuten könnte
-1173000 13,7 Nm --&gt; nachverspannt auf  17,1-17,2 Nm, bei 67 °C. Endlich herausgefunden, was ein Problem ist. Wenn der Prüfstand kalt ist, dann will er schnell auf die Prüfkastentemperatur hochheizen und überschätzt sich maßlos. Im Normalbetrieb ist die Aggregatstemperatur ca. 10 Kelvin höher. Beim Einrichten erreicht das Öl im Aggregat gerne 110°C oder mehr. Entsprechend muss beim korrekten Drehmoment einstellen vorab nur die Punpe aktiv sein, da sonst beim erneuten Einschalten die Öltemperatur im Prüfkasten über die eingestellte Hysterese schießt. Pumpe so lange Aktiv lassen, bis sich die Prüfkastentemperatur und Aggregattemperatur wieder angepasst haben. Dann Drehmoment erneut anpassen und losfahren.
-1194000 15,9 Nm --&gt; nicht nachverspannt, aber extrem schnell Drehmomentverlust, entsprechende Vermutung ab ca. 1 Mio starker abrasiver Verschleiß
-1120000 14,7 Nm --&gt; ZFB Zahn 31</t>
-  </si>
-  <si>
     <t>kst-E_72</t>
   </si>
   <si>
@@ -901,13 +891,6 @@
   </si>
   <si>
     <t>16,0-16,2</t>
-  </si>
-  <si>
-    <t>bei 68°C, nach paar Umdrehungen Temperatur auf 72° und 16,5-16,6 danach Drehmoment wieder abgefallen (Dieses Mal eingestellt bei Madenschraube oben) --&gt; nach 16min 16,0-16,2 bei 48000 und 71 °C trotz 67°C Ziel-Prüfkastentemperatur
-233000 15,4-15,5 Nm --&gt; nicht nachverspannt, bei 67 °C Prüfkastentemperatur und 77 °C Aggregattemperatur
-945000 13,7 Nm --&gt; nachverspannt auf 17,1-17,2 Nm, bei 69 °C, Ermüdung definitiv im Zahnfuß sichtbar und um Messzahn drei deutlich hellere Zähne
-1273000 13,7 Nm --&gt; nachverspannt auf 17,1-17,2 Nm, bei 70 °C, Ermüdung im Zahnfußbereich nicht wesentlich mehr, aber Verschleiß aufgrund Notwendigkeit vom Nachverspannen. Durchflussmenge angepasst, da wieder Übertemperatur. Durch deutliches Erhöhen des Durchflusses wurde weitere Verstopfung ausgeschlossen und auf 1,5 l/min bei neuer Düse eingestellt. Entsprechend sollte ein weiterer 16 Nm versucht geplant werden, damit bei frisch eingestellter Durchflussströmung die Schmierung gleich zu den neuen Versuchen zumindest bei einem der 16er Versuche gegeben ist, um Verschleiß mit Punktewolke gegenüberstellen zu können. --&gt; 1305000 16,7-16,8 Nm; 1327000 16,1-16,2 Nm; 1346000 15,4-15,5 Nm;
-1336000 14,8 Nm --&gt; Prüfstand ist sehr laut geworden --&gt; ZFB</t>
   </si>
   <si>
     <t>Durch Änderung des Temperatursensors beim Prüfkasten, andere Düse, und womöglich zu wenig Volumenstrom.
@@ -974,7 +957,31 @@
 6610000 6,8 Nm -&gt; nachverspannt auf 8,5-8,7 Nm bei TA 86 °C, TP 76 °C ;  (ca. 1 Nm Verlust über 2957000), Bilder aufgenommen. Leichte Haarrisse
 8410000 6,8 Nm -&gt; nachverspannt auf 8,6-8,7 Nm bei TA 91 °C, TP 77 °C ;  (ca. 1,7 Nm Verlust über 1800000), Bilder aufgenommen. Anrisse einzeln sichtbar.
 11161000 6,8 Nm -&gt; nachverspannt auf 8,2-8,4 Nm bei TA 93 °C, TP 77 °C ;  (ca. 1,8 Nm Verlust über 2751000), Bilder aufgenommen. Anrisse einzeln sichtbar, keine große Veränderung.
-14810000 6,8 Nm -&gt; nachverspannt auf 8,0-8,2 Nm bei TA 93 °C, TP 77 °C ;  (ca. 1,4 Nm Verlust über 3649000), Bilder aufgenommen. Anrisse deutlich sichtbar.</t>
+14810000 6,8 Nm -&gt; nachverspannt auf 8,0-8,2 Nm bei TA 93 °C, TP 77 °C ;  (ca. 1,4 Nm Verlust über 3649000), Bilder aufgenommen. Anrisse deutlich sichtbar.
+18365000 6,8 Nm -&gt; nachverspannt auf 8,5-8,6 Nm bei TA 83 °C, TP 75 °C; (ca. 1,2 Nm Verlust über 3555000), Bilder aufgenommen. Anrisse deutlich sichtbar. Beim Aufwärmen vollen Öldurchfluss, dadurch während Aufwärmen geringerer Temperaturunterscheid und kein überhitzen. Wieder zurück auf Markierung gestellt.
+22513000 7,1-7,2 bei TA 84 °C, TP 74 °C, 23417000 6,9-7,0 bei TA 84 °C, TP 74 °C
+23770000 6,8-7,0 Nm -&gt; nachverspannt auf 8,4-8,5 Nm bei TA 84 °C, TP 75 °C; (ca. 1,7 Nm Verlust über 5405000), Bilder aufgenommen. Anrisse deutlich sichtbar.
+Aber noch gar kein Versagensgeräusch hörbar. 27160000 7,6-7,7 bei TA 84 °C, TP 74 °C, minimales Versagensgeräusch zu hören, sehr sehr leise, Drehmoment schwankt noch nicht stark. 27600000 7,5-7,6 bei TA 84 °C, TP 74 °C, 30775000 7,1-7,2 bei TA 85 °C, TP 74 °C, Versagensgeräusch wird langsam lauter, 31915000 6,9-7,0 bei TA 83 °C, TP 74 °C,
+32015000 6,8-7,0 Nm -&gt; nachverspannt auf 7,9-8,0 Nm bei TA 81 °C, TP 75 °C; (ca. 1,6 Nm Verlust über 8245000), Bilder aufgenommen. Anrisse deutlich sichtbar.
+Noch keine Zähne locker. Versagensgeräusch wird lauter. Drehzahlsensor ausgefallen. aber Drehmomentschwlle erreicht. Entsprechend Schätzung auf 40000000
+Lastwechsel. Versagensgeräusch sehr laut, entsprechend Versuch beendet.</t>
+  </si>
+  <si>
+    <t>160000 15,2 Nm --&gt; nachverspannt auf 17,2-17,3 Nm, bei 72 °C obwohl steuerung auf 67 eingestellt
+962000 13,7 Nm --&gt; nachverspannt auf  16,5-16,7 Nm, bei 70 °C leichte Ermüdung im Zahnfußbereich zu sehen, aber eher hellere Zahnflächen, was auf Verschleiß hindeuten könnte
+1173000 13,7 Nm --&gt; nachverspannt auf  17,1-17,2 Nm, bei 67 °C. Endlich herausgefunden, was ein Problem ist. Wenn der Prüfstand kalt ist, dann will er schnell auf die Prüfkastentemperatur hochheizen und überschätzt sich maßlos. Im Normalbetrieb ist die Aggregatstemperatur ca. 10 Kelvin höher. Beim Einrichten erreicht das Öl im Aggregat gerne 110°C oder mehr. Entsprechend muss beim korrekten Drehmoment einstellen vorab nur die Punpe aktiv sein, da sonst beim erneuten Einschalten die Öltemperatur im Prüfkasten über die eingestellte Hysterese schießt. Pumpe so lange Aktiv lassen, bis sich die Prüfkastentemperatur und Aggregattemperatur wieder angepasst haben. Dann Drehmoment erneut anpassen und losfahren.
+1194000 15,9 Nm --&gt; nicht nachverspannt, aber extrem schnell Drehmomentverlust, entsprechende Vermutung ab ca. 1 Mio starker abrasiver Verschleiß
+1210000 14,7 Nm --&gt; ZFB Zahn 31</t>
+  </si>
+  <si>
+    <t>bei 68°C, nach paar Umdrehungen Temperatur auf 72° und 16,5-16,6 danach Drehmoment wieder abgefallen (Dieses Mal eingestellt bei Madenschraube oben) --&gt; nach 16min 16,0-16,2 bei 48000 und 71 °C trotz 67°C Ziel-Prüfkastentemperatur
+233000 15,4-15,5 Nm --&gt; nicht nachverspannt, bei 67 °C Prüfkastentemperatur und 77 °C Aggregattemperatur
+945000 13,7 Nm --&gt; nachverspannt auf 17,1-17,2 Nm, bei 69 °C, Ermüdung definitiv im Zahnfuß sichtbar und um Messzahn drei deutlich hellere Zähne
+1273000 13,7 Nm --&gt; nachverspannt auf 17,1-17,2 Nm, bei 70 °C, Ermüdung im Zahnfußbereich nicht wesentlich mehr, aber Verschleiß aufgrund Notwendigkeit vom Nachverspannen. Durchflussmenge angepasst, da wieder Übertemperatur. Durch deutliches Erhöhen des Durchflusses wurde weitere Verstopfung ausgeschlossen und auf 1,5 l/min bei neuer Düse eingestellt. Entsprechend sollte ein weiterer 16 Nm versucht geplant werden, damit bei frisch eingestellter Durchflussströmung die Schmierung gleich zu den neuen Versuchen zumindest bei einem der 16er Versuche gegeben ist, um Verschleiß mit Punktewolke gegenüberstellen zu können. --&gt; 1305000 16,7-16,8 Nm; 1327000 16,1-16,2 Nm; 1346000 15,4-15,5 Nm;
+1366000 14,8 Nm --&gt; Prüfstand ist sehr laut geworden --&gt; ZFB</t>
+  </si>
+  <si>
+    <t>sehr schwankend("ssc"): Stopp nach 2min (2 327), (ab ssc: 13,3…15,7bzw16,0Nm) (auch später: 13,1…15,0Nm) bis 36 349; (ab 13,9Nm…15,7Nm:) 304 112; (ab 13,4…15,8Nm:) 1 019 086; (ab 13,5…15,8Nm:) 1 909 028; (ab 14,0…15,4Nm:) 1 963 654; (ab 14,0...15,1:) 2 034 128</t>
   </si>
 </sst>
 </file>
@@ -1638,15 +1645,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1671,6 +1669,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2007,7 +2014,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3A9485-4D50-0041-9D5B-E8D35C0F1538}">
   <dimension ref="A1:U103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2016,7 +2023,7 @@
     <col min="5" max="5" width="6.83203125" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
     <col min="7" max="7" width="5.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="160" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="157" customWidth="1"/>
     <col min="9" max="9" width="5.5" customWidth="1"/>
     <col min="10" max="10" width="26.83203125" customWidth="1"/>
     <col min="11" max="11" width="8.6640625" customWidth="1"/>
@@ -2028,11 +2035,11 @@
     <col min="17" max="17" width="10.33203125" customWidth="1"/>
     <col min="18" max="18" width="9.1640625" customWidth="1"/>
     <col min="19" max="19" width="13.5" customWidth="1"/>
-    <col min="20" max="20" width="148" style="161" customWidth="1"/>
+    <col min="20" max="20" width="148" style="158" customWidth="1"/>
     <col min="21" max="21" width="195.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2095,7 +2102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -2138,7 +2145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
@@ -2178,7 +2185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2218,7 +2225,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
@@ -2258,7 +2265,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>31</v>
       </c>
@@ -2299,7 +2306,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" s="5" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
@@ -2355,7 +2362,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="14" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" s="14" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>36</v>
       </c>
@@ -2411,7 +2418,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="22" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="22" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
         <v>38</v>
       </c>
@@ -2468,7 +2475,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="29" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" s="29" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="27" t="s">
         <v>42</v>
       </c>
@@ -2528,7 +2535,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="34" t="s">
         <v>45</v>
       </c>
@@ -2588,7 +2595,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="27" t="s">
         <v>48</v>
       </c>
@@ -2648,7 +2655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="36" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="36" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="34" t="s">
         <v>51</v>
       </c>
@@ -2708,7 +2715,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="36" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" s="36" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="34" t="s">
         <v>54</v>
       </c>
@@ -2768,7 +2775,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="34" t="s">
         <v>57</v>
       </c>
@@ -2828,7 +2835,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="34" t="s">
         <v>61</v>
       </c>
@@ -2888,7 +2895,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="34" t="s">
         <v>65</v>
       </c>
@@ -2948,7 +2955,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="34" t="s">
         <v>68</v>
       </c>
@@ -3008,7 +3015,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="34" t="s">
         <v>71</v>
       </c>
@@ -3068,7 +3075,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="48" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" s="48" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="46" t="s">
         <v>74</v>
       </c>
@@ -3128,7 +3135,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="51" t="s">
         <v>78</v>
       </c>
@@ -3188,7 +3195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="34" t="s">
         <v>81</v>
       </c>
@@ -3248,7 +3255,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="57" t="s">
         <v>84</v>
       </c>
@@ -3308,7 +3315,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A24" s="64" t="s">
         <v>88</v>
       </c>
@@ -3368,7 +3375,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" s="74" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="70" t="s">
         <v>92</v>
       </c>
@@ -3428,7 +3435,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="82" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" s="82" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="78" t="s">
         <v>96</v>
       </c>
@@ -3488,7 +3495,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="85" t="s">
         <v>100</v>
       </c>
@@ -3548,7 +3555,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="85" t="s">
         <v>103</v>
       </c>
@@ -3608,7 +3615,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A29" s="91" t="s">
         <v>106</v>
       </c>
@@ -3668,7 +3675,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="91" t="s">
         <v>110</v>
       </c>
@@ -3728,7 +3735,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" s="74" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="70" t="s">
         <v>115</v>
       </c>
@@ -3788,7 +3795,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="101" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" s="101" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="99" t="s">
         <v>119</v>
       </c>
@@ -3848,7 +3855,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:20" s="108" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" s="108" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A33" s="106" t="s">
         <v>122</v>
       </c>
@@ -3908,7 +3915,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A34" s="112" t="s">
         <v>125</v>
       </c>
@@ -3965,12 +3972,12 @@
         <v>129</v>
       </c>
       <c r="T34" s="116" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" s="121" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="118" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" s="121" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="118" t="s">
-        <v>131</v>
       </c>
       <c r="B35" s="119">
         <v>45127</v>
@@ -4022,15 +4029,15 @@
         <v>4000</v>
       </c>
       <c r="S35" s="121" t="s">
+        <v>131</v>
+      </c>
+      <c r="T35" s="126" t="s">
         <v>132</v>
       </c>
-      <c r="T35" s="126" t="s">
+    </row>
+    <row r="36" spans="1:20" s="114" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="112" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" s="114" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="112" t="s">
-        <v>134</v>
       </c>
       <c r="B36" s="113">
         <v>45128</v>
@@ -4045,7 +4052,7 @@
         <v>86481</v>
       </c>
       <c r="F36" s="127" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G36" s="114">
         <v>76</v>
@@ -4054,10 +4061,10 @@
         <v>80</v>
       </c>
       <c r="I36" s="114" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J36" s="116" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K36" s="117">
         <v>14</v>
@@ -4066,10 +4073,10 @@
         <v>14.7</v>
       </c>
       <c r="M36" s="114" t="s">
+        <v>136</v>
+      </c>
+      <c r="N36" s="114" t="s">
         <v>137</v>
-      </c>
-      <c r="N36" s="114" t="s">
-        <v>138</v>
       </c>
       <c r="P36" s="114" t="s">
         <v>34</v>
@@ -4082,15 +4089,15 @@
         <v>1000</v>
       </c>
       <c r="S36" s="114" t="s">
+        <v>138</v>
+      </c>
+      <c r="T36" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="T36" s="114" t="s">
+    </row>
+    <row r="37" spans="1:20" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="85" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="85" t="s">
-        <v>141</v>
       </c>
       <c r="B37" s="86">
         <v>45135</v>
@@ -4142,15 +4149,15 @@
         <v>2250</v>
       </c>
       <c r="S37" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="T37" s="89" t="s">
         <v>142</v>
       </c>
-      <c r="T37" s="89" t="s">
+    </row>
+    <row r="38" spans="1:20" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="85" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="85" t="s">
-        <v>144</v>
       </c>
       <c r="B38" s="86">
         <v>45141</v>
@@ -4177,7 +4184,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K38" s="31">
         <v>16</v>
@@ -4202,15 +4209,15 @@
         <v>2250</v>
       </c>
       <c r="S38" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="T38" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="T38" s="30" t="s">
+    </row>
+    <row r="39" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="85" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="85" t="s">
-        <v>148</v>
       </c>
       <c r="B39" s="86">
         <v>45145</v>
@@ -4237,7 +4244,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="89" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K39" s="33">
         <v>18</v>
@@ -4262,15 +4269,15 @@
         <v>2250</v>
       </c>
       <c r="S39" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="T39" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="T39" s="89" t="s">
+    </row>
+    <row r="40" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="64" t="s">
         <v>150</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
-        <v>151</v>
       </c>
       <c r="B40" s="129">
         <v>45146</v>
@@ -4306,7 +4313,7 @@
         <v>14.7</v>
       </c>
       <c r="M40" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N40" s="40">
         <v>13</v>
@@ -4322,15 +4329,15 @@
         <v>3000</v>
       </c>
       <c r="S40" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="T40" s="69" t="s">
         <v>153</v>
       </c>
-      <c r="T40" s="69" t="s">
+    </row>
+    <row r="41" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="64" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="64" t="s">
-        <v>155</v>
       </c>
       <c r="B41" s="129">
         <v>45149</v>
@@ -4382,15 +4389,15 @@
         <v>2250</v>
       </c>
       <c r="S41" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="T41" s="69" t="s">
         <v>156</v>
       </c>
-      <c r="T41" s="69" t="s">
+    </row>
+    <row r="42" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="40" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="40" t="s">
-        <v>158</v>
       </c>
       <c r="B42" s="129">
         <v>45186</v>
@@ -4443,15 +4450,15 @@
         <v>2250</v>
       </c>
       <c r="S42" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="T42" s="69" t="s">
         <v>159</v>
       </c>
-      <c r="T42" s="69" t="s">
+    </row>
+    <row r="43" spans="1:20" s="82" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="78" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" s="82" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="78" t="s">
-        <v>161</v>
       </c>
       <c r="B43" s="79">
         <v>45193</v>
@@ -4478,7 +4485,7 @@
         <v>3</v>
       </c>
       <c r="J43" s="84" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K43" s="80">
         <v>12</v>
@@ -4506,12 +4513,12 @@
         <v>47883135</v>
       </c>
       <c r="T43" s="84" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" s="134" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="40" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" s="134" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="40" t="s">
-        <v>164</v>
       </c>
       <c r="B44" s="129"/>
       <c r="C44" s="36" t="s">
@@ -4559,12 +4566,12 @@
       </c>
       <c r="S44" s="38"/>
       <c r="T44" s="69" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="36" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="36" t="s">
-        <v>166</v>
       </c>
       <c r="B45" s="35"/>
       <c r="C45" s="36" t="s">
@@ -4598,9 +4605,9 @@
       </c>
       <c r="T45" s="38"/>
     </row>
-    <row r="46" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A46" s="114" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="113"/>
       <c r="C46" s="114" t="s">
@@ -4635,9 +4642,9 @@
       </c>
       <c r="T46" s="116"/>
     </row>
-    <row r="47" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A47" s="135" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="136"/>
       <c r="C47" s="135" t="s">
@@ -4659,9 +4666,9 @@
       </c>
       <c r="T47" s="139"/>
     </row>
-    <row r="48" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A48" s="135" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B48" s="136"/>
       <c r="C48" s="135" t="s">
@@ -4683,9 +4690,9 @@
       </c>
       <c r="T48" s="139"/>
     </row>
-    <row r="49" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="135" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="136"/>
       <c r="C49" s="135" t="s">
@@ -4703,14 +4710,14 @@
         <v>34</v>
       </c>
       <c r="Q49" s="135">
-        <f t="shared" ref="Q49:Q84" si="1">K49*1.0196</f>
+        <f t="shared" ref="Q49:Q85" si="1">K49*1.0196</f>
         <v>0</v>
       </c>
       <c r="T49" s="139"/>
     </row>
-    <row r="50" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="135" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B50" s="136"/>
       <c r="C50" s="135" t="s">
@@ -4734,15 +4741,15 @@
       <c r="R50" s="142"/>
       <c r="T50" s="139"/>
     </row>
-    <row r="51" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A51" s="135" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B51" s="136">
         <v>46094</v>
       </c>
       <c r="C51" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D51" s="135" t="s">
         <v>22</v>
@@ -4757,10 +4764,10 @@
         <v>86</v>
       </c>
       <c r="H51" s="135" t="s">
+        <v>173</v>
+      </c>
+      <c r="J51" s="135" t="s">
         <v>174</v>
-      </c>
-      <c r="J51" s="135" t="s">
-        <v>175</v>
       </c>
       <c r="K51" s="137">
         <v>7.9</v>
@@ -4785,18 +4792,18 @@
         <v>1945</v>
       </c>
       <c r="T51" s="139" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="135" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="135" t="s">
-        <v>177</v>
       </c>
       <c r="B52" s="136">
         <v>46104</v>
       </c>
       <c r="C52" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D52" s="135" t="s">
         <v>22</v>
@@ -4811,10 +4818,10 @@
         <v>86</v>
       </c>
       <c r="H52" s="135" t="s">
+        <v>173</v>
+      </c>
+      <c r="J52" s="135" t="s">
         <v>174</v>
-      </c>
-      <c r="J52" s="135" t="s">
-        <v>175</v>
       </c>
       <c r="K52" s="137">
         <v>7.9</v>
@@ -4839,18 +4846,18 @@
         <v>1945</v>
       </c>
       <c r="T52" s="139" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="135" t="s">
         <v>178</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="135" t="s">
-        <v>179</v>
       </c>
       <c r="B53" s="136">
         <v>46106</v>
       </c>
       <c r="C53" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D53" s="135" t="s">
         <v>22</v>
@@ -4865,10 +4872,10 @@
         <v>86</v>
       </c>
       <c r="H53" s="135" t="s">
+        <v>173</v>
+      </c>
+      <c r="J53" s="135" t="s">
         <v>174</v>
-      </c>
-      <c r="J53" s="135" t="s">
-        <v>175</v>
       </c>
       <c r="K53" s="137">
         <v>7.9</v>
@@ -4893,21 +4900,21 @@
         <v>1945</v>
       </c>
       <c r="T53" s="139" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="135" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="135" t="s">
-        <v>181</v>
       </c>
       <c r="B54" s="136">
         <v>46127</v>
       </c>
       <c r="C54" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D54" s="135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E54" s="135">
         <v>95919</v>
@@ -4945,19 +4952,19 @@
         <v>3058</v>
       </c>
       <c r="S54" s="135" t="s">
+        <v>182</v>
+      </c>
+      <c r="T54" s="139" t="s">
         <v>183</v>
       </c>
-      <c r="T54" s="139" t="s">
+    </row>
+    <row r="55" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="135" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="135" t="s">
-        <v>185</v>
       </c>
       <c r="B55" s="136"/>
       <c r="C55" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E55" s="135">
         <v>95919</v>
@@ -4979,13 +4986,13 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A56" s="135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B56" s="136"/>
       <c r="C56" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E56" s="135">
         <v>95919</v>
@@ -5003,13 +5010,13 @@
       </c>
       <c r="T56" s="139"/>
     </row>
-    <row r="57" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A57" s="135" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B57" s="136"/>
       <c r="C57" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E57" s="135">
         <v>95919</v>
@@ -5027,13 +5034,13 @@
       </c>
       <c r="T57" s="139"/>
     </row>
-    <row r="58" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A58" s="135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B58" s="136"/>
       <c r="C58" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E58" s="135">
         <v>95919</v>
@@ -5051,13 +5058,13 @@
       </c>
       <c r="T58" s="139"/>
     </row>
-    <row r="59" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A59" s="135" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B59" s="136"/>
       <c r="C59" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E59" s="135">
         <v>95919</v>
@@ -5076,13 +5083,13 @@
       </c>
       <c r="T59" s="139"/>
     </row>
-    <row r="60" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A60" s="135" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B60" s="136"/>
       <c r="C60" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E60" s="135">
         <v>95919</v>
@@ -5102,13 +5109,13 @@
       <c r="R60" s="142"/>
       <c r="T60" s="139"/>
     </row>
-    <row r="61" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A61" s="135" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B61" s="136"/>
       <c r="C61" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E61" s="135">
         <v>95919</v>
@@ -5126,13 +5133,13 @@
       </c>
       <c r="T61" s="139"/>
     </row>
-    <row r="62" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A62" s="135" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B62" s="136"/>
       <c r="C62" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E62" s="135">
         <v>95919</v>
@@ -5150,13 +5157,13 @@
       </c>
       <c r="T62" s="139"/>
     </row>
-    <row r="63" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A63" s="135" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B63" s="136"/>
       <c r="C63" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E63" s="135">
         <v>95919</v>
@@ -5174,18 +5181,18 @@
       </c>
       <c r="T63" s="139"/>
     </row>
-    <row r="64" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A64" s="135" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B64" s="136">
         <v>46139</v>
       </c>
       <c r="C64" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D64" s="135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E64" s="135">
         <v>95919</v>
@@ -5223,24 +5230,24 @@
         <v>3058</v>
       </c>
       <c r="S64" s="135" t="s">
+        <v>193</v>
+      </c>
+      <c r="T64" s="139" t="s">
         <v>194</v>
       </c>
-      <c r="T64" s="139" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A65" s="135" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B65" s="136">
         <v>46181</v>
       </c>
       <c r="C65" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D65" s="135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E65" s="135">
         <v>95919</v>
@@ -5280,24 +5287,24 @@
         <v>3058</v>
       </c>
       <c r="S65" s="135" t="s">
+        <v>195</v>
+      </c>
+      <c r="T65" s="139" t="s">
         <v>196</v>
       </c>
-      <c r="T65" s="139" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A66" s="135" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B66" s="136">
         <v>46217</v>
       </c>
       <c r="C66" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D66" s="135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E66" s="135">
         <v>95919</v>
@@ -5337,22 +5344,22 @@
         <v>3058</v>
       </c>
       <c r="S66" s="135" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="T66" s="139"/>
     </row>
-    <row r="67" spans="1:20" s="143" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" s="143" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="135" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B67" s="136">
         <v>46224</v>
       </c>
       <c r="C67" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D67" s="135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E67" s="135">
         <v>95919</v>
@@ -5368,7 +5375,7 @@
       </c>
       <c r="I67" s="135"/>
       <c r="J67" s="135" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K67" s="135">
         <v>9.8000000000000007</v>
@@ -5394,21 +5401,21 @@
         <v>3058</v>
       </c>
       <c r="S67" s="135" t="s">
+        <v>199</v>
+      </c>
+      <c r="T67" s="139" t="s">
         <v>200</v>
       </c>
-      <c r="T67" s="139" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A68" s="135" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B68" s="136">
         <v>46231</v>
       </c>
       <c r="C68" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D68" s="143" t="s">
         <v>29</v>
@@ -5451,21 +5458,21 @@
         <v>3058</v>
       </c>
       <c r="S68" s="135" t="s">
+        <v>201</v>
+      </c>
+      <c r="T68" s="139" t="s">
         <v>202</v>
       </c>
-      <c r="T68" s="139" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A69" s="135" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B69" s="136">
         <v>46233</v>
       </c>
       <c r="C69" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D69" s="135" t="s">
         <v>29</v>
@@ -5510,21 +5517,21 @@
         <v>3058</v>
       </c>
       <c r="S69" s="135" t="s">
+        <v>203</v>
+      </c>
+      <c r="T69" s="139" t="s">
         <v>204</v>
       </c>
-      <c r="T69" s="139" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A70" s="135" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B70" s="136">
         <v>46237</v>
       </c>
       <c r="C70" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D70" s="135" t="s">
         <v>29</v>
@@ -5569,21 +5576,21 @@
         <v>3058</v>
       </c>
       <c r="S70" s="135" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="T70" s="139" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A71" s="144" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B71" s="145">
         <v>46239</v>
       </c>
       <c r="C71" s="144" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D71" s="144" t="s">
         <v>29</v>
@@ -5628,18 +5635,18 @@
         <v>3058</v>
       </c>
       <c r="S71" s="144" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T71" s="147" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A72" s="135" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C72" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D72" s="135" t="s">
         <v>29</v>
@@ -5663,16 +5670,16 @@
       <c r="R72" s="135">
         <v>3058</v>
       </c>
-      <c r="T72" s="148" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T72" s="159" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A73" s="135" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C73" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D73" s="135" t="s">
         <v>29</v>
@@ -5696,14 +5703,14 @@
       <c r="R73" s="135">
         <v>3058</v>
       </c>
-      <c r="T73" s="149"/>
-    </row>
-    <row r="74" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T73" s="160"/>
+    </row>
+    <row r="74" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A74" s="135" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C74" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D74" s="135" t="s">
         <v>29</v>
@@ -5727,14 +5734,14 @@
       <c r="R74" s="135">
         <v>3058</v>
       </c>
-      <c r="T74" s="150"/>
-    </row>
-    <row r="75" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="T74" s="161"/>
+    </row>
+    <row r="75" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A75" s="135" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C75" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D75" s="135" t="s">
         <v>29</v>
@@ -5759,19 +5766,19 @@
         <v>3058</v>
       </c>
       <c r="S75" s="135" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="T75" s="139"/>
     </row>
-    <row r="76" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A76" s="135" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B76" s="136">
         <v>46247</v>
       </c>
       <c r="C76" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D76" s="135" t="s">
         <v>29</v>
@@ -5808,320 +5815,320 @@
         <v>3058</v>
       </c>
       <c r="S76" s="135" t="s">
+        <v>208</v>
+      </c>
+      <c r="T76" s="139" t="s">
         <v>209</v>
       </c>
-      <c r="T76" s="139" t="s">
+    </row>
+    <row r="77" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="148" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="151" t="s">
+      <c r="B77" s="149">
+        <v>46252</v>
+      </c>
+      <c r="C77" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D77" s="148" t="s">
         <v>211</v>
       </c>
-      <c r="B77" s="152">
-        <v>46252</v>
-      </c>
-      <c r="C77" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" s="151" t="s">
+      <c r="E77" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F77" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G77" s="148">
+        <v>75</v>
+      </c>
+      <c r="H77" s="150">
+        <v>80</v>
+      </c>
+      <c r="K77" s="148">
+        <v>11.8</v>
+      </c>
+      <c r="M77" s="148" t="s">
         <v>212</v>
       </c>
-      <c r="E77" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F77" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G77" s="151">
-        <v>75</v>
-      </c>
-      <c r="H77" s="153">
-        <v>80</v>
-      </c>
-      <c r="K77" s="151">
-        <v>11.8</v>
-      </c>
-      <c r="M77" s="151" t="s">
+      <c r="N77" s="148" t="s">
         <v>213</v>
       </c>
-      <c r="N77" s="151" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q77" s="151">
+      <c r="Q77" s="148">
         <f t="shared" si="1"/>
         <v>12.031280000000001</v>
       </c>
-      <c r="R77" s="151">
+      <c r="R77" s="148">
         <v>2294</v>
       </c>
-      <c r="S77" s="151">
+      <c r="S77" s="148">
         <v>149937</v>
       </c>
-      <c r="T77" s="154" t="s">
+      <c r="T77" s="151" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B78" s="149">
+        <v>46252</v>
+      </c>
+      <c r="C78" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F78" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G78" s="148">
+        <v>75</v>
+      </c>
+      <c r="H78" s="150">
+        <v>80</v>
+      </c>
+      <c r="K78" s="148">
+        <v>11.8</v>
+      </c>
+      <c r="M78" s="148" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="152">
-        <v>46252</v>
-      </c>
-      <c r="C78" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D78" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E78" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F78" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G78" s="151">
-        <v>75</v>
-      </c>
-      <c r="H78" s="153">
-        <v>80</v>
-      </c>
-      <c r="K78" s="151">
-        <v>11.8</v>
-      </c>
-      <c r="M78" s="151" t="s">
-        <v>216</v>
-      </c>
-      <c r="N78" s="151" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q78" s="151">
+      <c r="N78" s="148" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q78" s="148">
         <f t="shared" si="1"/>
         <v>12.031280000000001</v>
       </c>
-      <c r="R78" s="151">
+      <c r="R78" s="148">
         <v>3058</v>
       </c>
-      <c r="S78" s="151" t="s">
+      <c r="S78" s="148" t="s">
+        <v>216</v>
+      </c>
+      <c r="T78" s="151" t="s">
         <v>217</v>
       </c>
-      <c r="T78" s="154" t="s">
+    </row>
+    <row r="79" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B79" s="149">
+        <v>46252</v>
+      </c>
+      <c r="C79" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E79" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F79" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G79" s="148">
+        <v>75</v>
+      </c>
+      <c r="H79" s="150">
+        <v>80</v>
+      </c>
+      <c r="K79" s="148">
+        <v>7.9</v>
+      </c>
+      <c r="M79" s="148" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="152">
-        <v>46252</v>
-      </c>
-      <c r="C79" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D79" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E79" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F79" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G79" s="151">
-        <v>75</v>
-      </c>
-      <c r="H79" s="153">
-        <v>80</v>
-      </c>
-      <c r="K79" s="151">
-        <v>7.9</v>
-      </c>
-      <c r="M79" s="151" t="s">
+      <c r="N79" s="148" t="s">
         <v>219</v>
       </c>
-      <c r="N79" s="151" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q79" s="151">
+      <c r="Q79" s="148">
         <f t="shared" si="1"/>
         <v>8.0548400000000004</v>
       </c>
-      <c r="R79" s="151">
+      <c r="R79" s="148">
         <v>2294</v>
       </c>
-      <c r="T79" s="154" t="s">
+      <c r="T79" s="151" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B80" s="149">
+        <v>46252</v>
+      </c>
+      <c r="C80" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D80" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F80" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G80" s="148">
+        <v>75</v>
+      </c>
+      <c r="H80" s="150">
+        <v>80</v>
+      </c>
+      <c r="K80" s="148">
+        <v>7.8</v>
+      </c>
+      <c r="M80" s="148" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="152">
-        <v>46252</v>
-      </c>
-      <c r="C80" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D80" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E80" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F80" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G80" s="151">
-        <v>75</v>
-      </c>
-      <c r="H80" s="153">
-        <v>80</v>
-      </c>
-      <c r="K80" s="151">
-        <v>7.8</v>
-      </c>
-      <c r="M80" s="151" t="s">
-        <v>222</v>
-      </c>
-      <c r="N80" s="151" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q80" s="151">
+      <c r="N80" s="148" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q80" s="148">
         <f t="shared" si="1"/>
         <v>7.9528800000000004</v>
       </c>
-      <c r="R80" s="151">
+      <c r="R80" s="148">
         <v>3058</v>
       </c>
-      <c r="T80" s="154" t="s">
+      <c r="T80" s="151" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B81" s="149">
+        <v>46253</v>
+      </c>
+      <c r="C81" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D81" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E81" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F81" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G81" s="148">
+        <v>75</v>
+      </c>
+      <c r="H81" s="150">
+        <v>80</v>
+      </c>
+      <c r="K81" s="148">
+        <v>15.7</v>
+      </c>
+      <c r="M81" s="148" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="152">
-        <v>46253</v>
-      </c>
-      <c r="C81" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D81" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E81" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F81" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G81" s="151">
-        <v>75</v>
-      </c>
-      <c r="H81" s="153">
-        <v>80</v>
-      </c>
-      <c r="K81" s="151">
-        <v>15.7</v>
-      </c>
-      <c r="M81" s="151" t="s">
+      <c r="N81" s="148" t="s">
         <v>224</v>
       </c>
-      <c r="N81" s="151" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q81" s="151">
+      <c r="Q81" s="148">
         <f t="shared" si="1"/>
         <v>16.007719999999999</v>
       </c>
-      <c r="R81" s="151">
+      <c r="R81" s="148">
         <v>2294</v>
       </c>
-      <c r="S81" s="151">
+      <c r="S81" s="148">
         <v>1225086</v>
       </c>
-      <c r="T81" s="154" t="s">
+      <c r="T81" s="151" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B82" s="149">
+        <v>46253</v>
+      </c>
+      <c r="C82" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D82" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E82" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F82" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G82" s="148">
+        <v>75</v>
+      </c>
+      <c r="H82" s="150">
+        <v>80</v>
+      </c>
+      <c r="K82" s="148">
+        <v>15.7</v>
+      </c>
+      <c r="M82" s="148" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="152">
-        <v>46253</v>
-      </c>
-      <c r="C82" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D82" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E82" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F82" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G82" s="151">
-        <v>75</v>
-      </c>
-      <c r="H82" s="153">
-        <v>80</v>
-      </c>
-      <c r="K82" s="151">
-        <v>15.7</v>
-      </c>
-      <c r="M82" s="151" t="s">
+      <c r="N82" s="148" t="s">
         <v>227</v>
       </c>
-      <c r="N82" s="151" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q82" s="151">
+      <c r="Q82" s="148">
         <f t="shared" si="1"/>
         <v>16.007719999999999</v>
       </c>
-      <c r="R82" s="151">
+      <c r="R82" s="148">
         <v>3058</v>
       </c>
-      <c r="S82" s="151">
+      <c r="S82" s="148">
         <v>1550274</v>
       </c>
-      <c r="T82" s="154" t="s">
+      <c r="T82" s="151" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B83" s="149">
+        <v>46255</v>
+      </c>
+      <c r="C83" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D83" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E83" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F83" s="148">
+        <v>97351</v>
+      </c>
+      <c r="G83" s="148">
+        <v>75</v>
+      </c>
+      <c r="H83" s="150">
+        <v>80</v>
+      </c>
+      <c r="R83" s="148">
+        <v>3058</v>
+      </c>
+      <c r="S83" s="148">
+        <v>2424628</v>
+      </c>
+      <c r="T83" s="151" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="83" spans="1:21" s="151" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B83" s="152">
-        <v>46255</v>
-      </c>
-      <c r="C83" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D83" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E83" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F83" s="151">
-        <v>97351</v>
-      </c>
-      <c r="G83" s="151">
-        <v>75</v>
-      </c>
-      <c r="H83" s="153">
-        <v>80</v>
-      </c>
-      <c r="R83" s="151">
-        <v>3058</v>
-      </c>
-      <c r="S83" s="151">
-        <v>2424628</v>
-      </c>
-      <c r="T83" s="154" t="s">
+    <row r="84" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="135" t="s">
         <v>230</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="135" t="s">
-        <v>231</v>
       </c>
       <c r="B84" s="136">
         <v>46258</v>
       </c>
       <c r="C84" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D84" s="135" t="s">
         <v>29</v>
@@ -6158,18 +6165,18 @@
         <v>1671472</v>
       </c>
       <c r="T84" s="139" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="135" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="135" t="s">
-        <v>233</v>
       </c>
       <c r="B85" s="136">
         <v>46259</v>
       </c>
       <c r="C85" s="135" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D85" s="135" t="s">
         <v>29</v>
@@ -6198,81 +6205,88 @@
       <c r="N85" s="135">
         <v>13.1</v>
       </c>
+      <c r="Q85" s="135">
+        <f t="shared" si="1"/>
+        <v>13.999108000000001</v>
+      </c>
+      <c r="R85" s="135">
+        <v>3058</v>
+      </c>
       <c r="S85" s="135">
         <v>27610155</v>
       </c>
       <c r="T85" s="139" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" s="148" customFormat="1" ht="32" x14ac:dyDescent="0.4">
+      <c r="A86" s="148" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" s="151" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A86" s="151" t="s">
+      <c r="B86" s="149">
+        <v>46252</v>
+      </c>
+      <c r="C86" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D86" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E86" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F86" s="148">
+        <v>97350</v>
+      </c>
+      <c r="G86" s="148">
+        <v>74</v>
+      </c>
+      <c r="H86" s="150">
+        <v>80</v>
+      </c>
+      <c r="K86" s="148">
+        <v>11.8</v>
+      </c>
+      <c r="M86" s="148" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="152">
-        <v>46252</v>
-      </c>
-      <c r="C86" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D86" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E86" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F86" s="151">
-        <v>97350</v>
-      </c>
-      <c r="G86" s="151">
-        <v>74</v>
-      </c>
-      <c r="H86" s="153">
-        <v>80</v>
-      </c>
-      <c r="K86" s="151">
-        <v>11.8</v>
-      </c>
-      <c r="M86" s="151" t="s">
+      <c r="N86" s="148" t="s">
         <v>236</v>
       </c>
-      <c r="N86" s="151" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q86" s="151">
+      <c r="Q86" s="148">
         <f t="shared" ref="Q86" si="2">K86*1.0196</f>
         <v>12.031280000000001</v>
       </c>
-      <c r="R86" s="151">
+      <c r="R86" s="148">
         <v>3058</v>
       </c>
-      <c r="S86" s="151">
+      <c r="S86" s="148">
         <v>6213262</v>
       </c>
-      <c r="T86" s="155" t="s">
+      <c r="T86" s="152" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" s="143" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="153" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" s="143" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="156" t="s">
-        <v>239</v>
-      </c>
-      <c r="B87" s="157">
+      <c r="B87" s="154">
         <v>46269</v>
       </c>
       <c r="C87" s="135" t="s">
-        <v>173</v>
-      </c>
-      <c r="D87" s="156" t="s">
+        <v>172</v>
+      </c>
+      <c r="D87" s="153" t="s">
         <v>22</v>
       </c>
       <c r="E87" s="135">
         <v>95919</v>
       </c>
-      <c r="F87" s="156">
+      <c r="F87" s="153">
         <v>95878</v>
       </c>
-      <c r="G87" s="156">
+      <c r="G87" s="153">
         <v>75</v>
       </c>
       <c r="H87" s="140">
@@ -6280,482 +6294,485 @@
       </c>
       <c r="I87" s="135"/>
       <c r="J87" s="135"/>
-      <c r="K87" s="156">
+      <c r="K87" s="153">
         <v>9.8000000000000007</v>
       </c>
       <c r="L87" s="135">
         <v>13</v>
       </c>
-      <c r="M87" s="156">
+      <c r="M87" s="153">
         <v>10.1</v>
       </c>
-      <c r="N87" s="156" t="s">
-        <v>217</v>
-      </c>
-      <c r="O87" s="156"/>
-      <c r="P87" s="156"/>
-      <c r="Q87" s="156"/>
+      <c r="N87" s="153" t="s">
+        <v>216</v>
+      </c>
+      <c r="O87" s="153"/>
+      <c r="P87" s="153"/>
+      <c r="Q87" s="153"/>
       <c r="R87" s="135">
         <v>3058</v>
       </c>
-      <c r="S87" s="156" t="s">
+      <c r="S87" s="153" t="s">
+        <v>239</v>
+      </c>
+      <c r="T87" s="155" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" s="148" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+      <c r="A88" s="148" t="s">
         <v>240</v>
       </c>
-      <c r="T87" s="158" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" s="151" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A88" s="151" t="s">
+      <c r="B88" s="149">
+        <v>46272</v>
+      </c>
+      <c r="C88" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E88" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F88" s="148">
+        <v>97365</v>
+      </c>
+      <c r="G88" s="148">
+        <v>74</v>
+      </c>
+      <c r="H88" s="150">
+        <v>80</v>
+      </c>
+      <c r="J88" s="148" t="s">
         <v>241</v>
       </c>
-      <c r="B88" s="152">
-        <v>46272</v>
-      </c>
-      <c r="C88" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D88" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E88" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F88" s="151">
-        <v>97365</v>
-      </c>
-      <c r="G88" s="151">
-        <v>74</v>
-      </c>
-      <c r="H88" s="153">
-        <v>80</v>
-      </c>
-      <c r="J88" s="151" t="s">
+      <c r="K88" s="148">
+        <v>11.8</v>
+      </c>
+      <c r="L88" s="148">
+        <v>13.9</v>
+      </c>
+      <c r="M88" s="148" t="s">
         <v>242</v>
       </c>
-      <c r="K88" s="151">
-        <v>11.8</v>
-      </c>
-      <c r="L88" s="151">
-        <v>13.9</v>
-      </c>
-      <c r="M88" s="151" t="s">
+      <c r="N88" s="148" t="s">
         <v>243</v>
       </c>
-      <c r="N88" s="151" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q88" s="151">
+      <c r="Q88" s="148">
         <f t="shared" ref="Q88:Q92" si="3">K88*(52/51)</f>
         <v>12.031372549019608</v>
       </c>
-      <c r="R88" s="151">
+      <c r="R88" s="148">
         <v>3058</v>
       </c>
-      <c r="S88" s="151">
+      <c r="S88" s="148">
         <v>3776250</v>
       </c>
-      <c r="T88" s="155" t="s">
+      <c r="T88" s="152" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" s="148" customFormat="1" ht="240" x14ac:dyDescent="0.4">
+      <c r="A89" s="148" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" s="151" customFormat="1" ht="255" x14ac:dyDescent="0.2">
-      <c r="A89" s="151" t="s">
+      <c r="B89" s="149">
+        <v>46279</v>
+      </c>
+      <c r="C89" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D89" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F89" s="148">
+        <v>97345</v>
+      </c>
+      <c r="G89" s="148">
+        <v>74</v>
+      </c>
+      <c r="H89" s="150">
+        <v>80</v>
+      </c>
+      <c r="J89" s="148" t="s">
         <v>246</v>
       </c>
-      <c r="B89" s="152">
-        <v>46279</v>
-      </c>
-      <c r="C89" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D89" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E89" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F89" s="151">
-        <v>97345</v>
-      </c>
-      <c r="G89" s="151">
-        <v>74</v>
-      </c>
-      <c r="H89" s="153">
-        <v>80</v>
-      </c>
-      <c r="J89" s="151" t="s">
+      <c r="K89" s="148">
+        <v>7.9</v>
+      </c>
+      <c r="L89" s="148">
+        <v>11.1</v>
+      </c>
+      <c r="M89" s="148" t="s">
         <v>247</v>
       </c>
-      <c r="K89" s="151">
-        <v>7.9</v>
-      </c>
-      <c r="L89" s="151">
-        <v>11.1</v>
-      </c>
-      <c r="M89" s="151" t="s">
+      <c r="N89" s="156" t="s">
         <v>248</v>
       </c>
-      <c r="N89" s="159" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q89" s="151">
+      <c r="Q89" s="148">
         <f t="shared" si="3"/>
         <v>8.0549019607843135</v>
       </c>
-      <c r="R89" s="151">
+      <c r="R89" s="148">
         <v>3058</v>
       </c>
-      <c r="S89" s="151">
+      <c r="S89" s="148">
         <v>24956000</v>
       </c>
-      <c r="T89" s="155" t="s">
+      <c r="T89" s="152" t="s">
+        <v>249</v>
+      </c>
+      <c r="U89" s="148" t="s">
         <v>250</v>
       </c>
-      <c r="U89" s="151" t="s">
+    </row>
+    <row r="90" spans="1:21" s="148" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+      <c r="A90" s="148" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" s="151" customFormat="1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A90" s="151" t="s">
+      <c r="B90" s="149">
+        <v>46286</v>
+      </c>
+      <c r="C90" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D90" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F90" s="148">
+        <v>97346</v>
+      </c>
+      <c r="G90" s="148">
+        <v>67</v>
+      </c>
+      <c r="H90" s="150">
+        <v>80</v>
+      </c>
+      <c r="J90" s="156" t="s">
         <v>252</v>
       </c>
-      <c r="B90" s="152">
-        <v>46286</v>
-      </c>
-      <c r="C90" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D90" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E90" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F90" s="151">
-        <v>97346</v>
-      </c>
-      <c r="G90" s="151">
-        <v>67</v>
-      </c>
-      <c r="H90" s="153">
-        <v>80</v>
-      </c>
-      <c r="J90" s="159" t="s">
-        <v>253</v>
-      </c>
-      <c r="K90" s="151">
+      <c r="K90" s="148">
         <v>15.7</v>
       </c>
-      <c r="L90" s="151">
+      <c r="L90" s="148">
         <v>17</v>
       </c>
-      <c r="M90" s="151">
+      <c r="M90" s="148">
         <v>15.5</v>
       </c>
-      <c r="N90" s="151">
+      <c r="N90" s="148">
         <v>14.9</v>
       </c>
-      <c r="Q90" s="151">
+      <c r="Q90" s="148">
         <f t="shared" si="3"/>
         <v>16.007843137254898</v>
       </c>
-      <c r="R90" s="151">
+      <c r="R90" s="148">
         <v>3058</v>
       </c>
-      <c r="S90" s="151">
+      <c r="S90" s="148">
         <v>1512000</v>
       </c>
-      <c r="T90" s="155" t="s">
+      <c r="T90" s="152" t="s">
+        <v>253</v>
+      </c>
+      <c r="U90" s="148" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" s="148" customFormat="1" ht="240" x14ac:dyDescent="0.4">
+      <c r="A91" s="148" t="s">
         <v>254</v>
       </c>
-      <c r="U90" s="151" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" s="151" customFormat="1" ht="255" x14ac:dyDescent="0.2">
-      <c r="A91" s="151" t="s">
+      <c r="B91" s="149">
+        <v>46287</v>
+      </c>
+      <c r="C91" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D91" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E91" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F91" s="148">
+        <v>97366</v>
+      </c>
+      <c r="G91" s="148">
+        <v>67</v>
+      </c>
+      <c r="H91" s="150">
+        <v>80</v>
+      </c>
+      <c r="J91" s="156" t="s">
         <v>255</v>
       </c>
-      <c r="B91" s="152">
-        <v>46287</v>
-      </c>
-      <c r="C91" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D91" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E91" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F91" s="151">
-        <v>97366</v>
-      </c>
-      <c r="G91" s="151">
-        <v>67</v>
-      </c>
-      <c r="H91" s="153">
-        <v>80</v>
-      </c>
-      <c r="J91" s="159" t="s">
+      <c r="K91" s="148">
+        <v>15.7</v>
+      </c>
+      <c r="L91" s="148">
+        <v>17.2</v>
+      </c>
+      <c r="M91" s="148" t="s">
         <v>256</v>
       </c>
-      <c r="K91" s="151">
-        <v>15.7</v>
-      </c>
-      <c r="L91" s="151">
-        <v>17.2</v>
-      </c>
-      <c r="M91" s="151" t="s">
-        <v>257</v>
-      </c>
-      <c r="N91" s="151">
+      <c r="N91" s="148">
         <v>15.5</v>
       </c>
-      <c r="Q91" s="151">
+      <c r="Q91" s="148">
         <f t="shared" si="3"/>
         <v>16.007843137254898</v>
       </c>
-      <c r="R91" s="151">
+      <c r="R91" s="148">
         <v>3058</v>
       </c>
-      <c r="S91" s="151">
-        <v>1120000</v>
-      </c>
-      <c r="T91" s="155" t="s">
+      <c r="S91" s="148">
+        <v>1210000</v>
+      </c>
+      <c r="T91" s="152" t="s">
+        <v>275</v>
+      </c>
+      <c r="U91" s="148" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" s="148" customFormat="1" ht="160" x14ac:dyDescent="0.4">
+      <c r="A92" s="148" t="s">
+        <v>257</v>
+      </c>
+      <c r="B92" s="149">
+        <v>46288</v>
+      </c>
+      <c r="C92" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D92" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E92" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F92" s="148">
+        <v>97355</v>
+      </c>
+      <c r="G92" s="148">
+        <v>67</v>
+      </c>
+      <c r="H92" s="150">
+        <v>80</v>
+      </c>
+      <c r="J92" s="156" t="s">
         <v>258</v>
       </c>
-      <c r="U91" s="151" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" s="151" customFormat="1" ht="170" x14ac:dyDescent="0.2">
-      <c r="A92" s="151" t="s">
+      <c r="K92" s="148">
+        <v>15.7</v>
+      </c>
+      <c r="L92" s="148">
+        <v>16.5</v>
+      </c>
+      <c r="M92" s="156" t="s">
         <v>259</v>
       </c>
-      <c r="B92" s="152">
-        <v>46288</v>
-      </c>
-      <c r="C92" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D92" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E92" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F92" s="151">
-        <v>97355</v>
-      </c>
-      <c r="G92" s="151">
-        <v>67</v>
-      </c>
-      <c r="H92" s="153">
-        <v>80</v>
-      </c>
-      <c r="J92" s="159" t="s">
+      <c r="N92" s="148" t="s">
         <v>260</v>
       </c>
-      <c r="K92" s="151">
-        <v>15.7</v>
-      </c>
-      <c r="L92" s="151">
-        <v>16.5</v>
-      </c>
-      <c r="M92" s="159" t="s">
-        <v>261</v>
-      </c>
-      <c r="N92" s="151" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q92" s="151">
+      <c r="Q92" s="148">
         <f t="shared" si="3"/>
         <v>16.007843137254898</v>
       </c>
-      <c r="R92" s="151">
+      <c r="R92" s="148">
         <v>3058</v>
       </c>
-      <c r="S92" s="151">
-        <v>1336000</v>
-      </c>
-      <c r="T92" s="155" t="s">
+      <c r="S92" s="148">
+        <v>1366000</v>
+      </c>
+      <c r="T92" s="152" t="s">
+        <v>276</v>
+      </c>
+      <c r="U92" s="148" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" s="148" customFormat="1" ht="128" x14ac:dyDescent="0.4">
+      <c r="A93" s="148" t="s">
+        <v>262</v>
+      </c>
+      <c r="B93" s="149">
+        <v>46289</v>
+      </c>
+      <c r="C93" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D93" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E93" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F93" s="148">
+        <v>97340</v>
+      </c>
+      <c r="G93" s="148">
+        <v>67</v>
+      </c>
+      <c r="H93" s="150">
+        <v>80</v>
+      </c>
+      <c r="J93" s="156" t="s">
         <v>263</v>
       </c>
-      <c r="U92" s="151" t="s">
+      <c r="K93" s="148">
+        <v>15.7</v>
+      </c>
+      <c r="L93" s="148">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="M93" s="156" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" s="151" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A93" s="151" t="s">
+      <c r="N93" s="148" t="s">
         <v>265</v>
       </c>
-      <c r="B93" s="152">
-        <v>46289</v>
-      </c>
-      <c r="C93" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D93" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E93" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F93" s="151">
-        <v>97340</v>
-      </c>
-      <c r="G93" s="151">
-        <v>67</v>
-      </c>
-      <c r="H93" s="153">
-        <v>80</v>
-      </c>
-      <c r="J93" s="159" t="s">
-        <v>266</v>
-      </c>
-      <c r="K93" s="151">
-        <v>15.7</v>
-      </c>
-      <c r="L93" s="151">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="M93" s="159" t="s">
-        <v>267</v>
-      </c>
-      <c r="N93" s="151" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q93" s="151">
+      <c r="Q93" s="148">
         <f>K93*(52/51)</f>
         <v>16.007843137254898</v>
       </c>
-      <c r="R93" s="151">
+      <c r="R93" s="148">
         <v>3058</v>
       </c>
-      <c r="S93" s="151">
+      <c r="S93" s="148">
         <v>1920000</v>
       </c>
-      <c r="T93" s="155" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" s="151" customFormat="1" ht="272" x14ac:dyDescent="0.2">
-      <c r="A94" s="151" t="s">
-        <v>270</v>
-      </c>
-      <c r="B94" s="152">
+      <c r="T93" s="152" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" s="148" customFormat="1" ht="256" x14ac:dyDescent="0.4">
+      <c r="A94" s="148" t="s">
+        <v>267</v>
+      </c>
+      <c r="B94" s="149">
         <v>46290</v>
       </c>
-      <c r="C94" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D94" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E94" s="151">
+      <c r="C94" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D94" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E94" s="148">
         <v>95919</v>
       </c>
-      <c r="F94" s="151">
+      <c r="F94" s="148">
         <v>97360</v>
       </c>
-      <c r="G94" s="151">
+      <c r="G94" s="148">
         <v>74</v>
       </c>
-      <c r="H94" s="153">
-        <v>80</v>
-      </c>
-      <c r="J94" s="159" t="s">
-        <v>242</v>
-      </c>
-      <c r="K94" s="151">
+      <c r="H94" s="150">
+        <v>80</v>
+      </c>
+      <c r="J94" s="156" t="s">
+        <v>241</v>
+      </c>
+      <c r="K94" s="148">
         <v>11.8</v>
       </c>
-      <c r="L94" s="151">
+      <c r="L94" s="148">
         <v>14.9</v>
       </c>
-      <c r="M94" s="159" t="s">
-        <v>244</v>
-      </c>
-      <c r="N94" s="151" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q94" s="151">
+      <c r="M94" s="156" t="s">
+        <v>243</v>
+      </c>
+      <c r="N94" s="148" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q94" s="148">
         <f>K94*(52/51)</f>
         <v>12.031372549019608</v>
       </c>
-      <c r="R94" s="151">
+      <c r="R94" s="148">
         <v>3058</v>
       </c>
-      <c r="S94" s="151">
+      <c r="S94" s="148">
         <v>4570000</v>
       </c>
-      <c r="T94" s="155" t="s">
+      <c r="T94" s="152" t="s">
+        <v>269</v>
+      </c>
+      <c r="U94" s="156" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" s="148" customFormat="1" ht="272" x14ac:dyDescent="0.4">
+      <c r="A95" s="148" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="149">
+        <v>46293</v>
+      </c>
+      <c r="C95" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D95" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F95" s="148">
+        <v>97364</v>
+      </c>
+      <c r="G95" s="148">
+        <v>75</v>
+      </c>
+      <c r="H95" s="150">
+        <v>80</v>
+      </c>
+      <c r="J95" s="156"/>
+      <c r="K95" s="148">
+        <v>7.8</v>
+      </c>
+      <c r="L95" s="148">
+        <v>11.1</v>
+      </c>
+      <c r="M95" s="156" t="s">
         <v>272</v>
       </c>
-      <c r="U94" s="159" t="s">
+      <c r="N95" s="148" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" s="151" customFormat="1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A95" s="151" t="s">
-        <v>274</v>
-      </c>
-      <c r="B95" s="152">
-        <v>46293</v>
-      </c>
-      <c r="C95" s="151" t="s">
-        <v>173</v>
-      </c>
-      <c r="D95" s="151" t="s">
-        <v>212</v>
-      </c>
-      <c r="E95" s="151">
-        <v>95919</v>
-      </c>
-      <c r="F95" s="151">
-        <v>97364</v>
-      </c>
-      <c r="G95" s="151">
-        <v>75</v>
-      </c>
-      <c r="H95" s="153">
-        <v>80</v>
-      </c>
-      <c r="J95" s="159"/>
-      <c r="K95" s="151">
-        <v>7.8</v>
-      </c>
-      <c r="L95" s="151">
-        <v>11.1</v>
-      </c>
-      <c r="M95" s="159" t="s">
-        <v>275</v>
-      </c>
-      <c r="N95" s="151" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q95" s="151">
+      <c r="Q95" s="148">
         <f>K95*(52/51)</f>
         <v>7.9529411764705875</v>
       </c>
-      <c r="R95" s="151">
+      <c r="R95" s="148">
         <v>3058</v>
       </c>
-      <c r="T95" s="155" t="s">
-        <v>277</v>
-      </c>
-      <c r="U95" s="159"/>
-    </row>
-    <row r="97" spans="20:20" x14ac:dyDescent="0.2">
-      <c r="T97" s="161" t="s">
+      <c r="S95" s="148">
+        <v>40000000</v>
+      </c>
+      <c r="T95" s="152" t="s">
+        <v>274</v>
+      </c>
+      <c r="U95" s="156"/>
+    </row>
+    <row r="97" spans="20:20" x14ac:dyDescent="0.4">
+      <c r="T97" s="158" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="103" spans="20:20" x14ac:dyDescent="0.2">
-      <c r="T103" s="161" t="s">
-        <v>217</v>
+    <row r="103" spans="20:20" x14ac:dyDescent="0.4">
+      <c r="T103" s="158" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/70_input/72_Kleingetriebepruefstand_KV3/kst-E_Laufversuche_KV3.xlsx
+++ b/70_input/72_Kleingetriebepruefstand_KV3/kst-E_Laufversuche_KV3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub-tkuhn39\semesterthesis\70_input\72_Kleingetriebepruefstand_KV3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D51430-287A-45D1-8DC7-9A3CD7F5BD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA3F3D2-2F77-4BAF-938D-4B350E82F015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{09DE1DE6-8CB8-D84C-8367-607651AAD6B1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{09DE1DE6-8CB8-D84C-8367-607651AAD6B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="280">
   <si>
     <t>A</t>
   </si>
@@ -982,6 +982,15 @@
   </si>
   <si>
     <t>sehr schwankend("ssc"): Stopp nach 2min (2 327), (ab ssc: 13,3…15,7bzw16,0Nm) (auch später: 13,1…15,0Nm) bis 36 349; (ab 13,9Nm…15,7Nm:) 304 112; (ab 13,4…15,8Nm:) 1 019 086; (ab 13,5…15,8Nm:) 1 909 028; (ab 14,0…15,4Nm:) 1 963 654; (ab 14,0...15,1:) 2 034 128</t>
+  </si>
+  <si>
+    <t>kst-E_76</t>
+  </si>
+  <si>
+    <t>... 6,8 Nm -&gt; nachverspannt auf ... Nm bei TA ... °C, TP ... °C ;  (ca. ... Nm Verlust über ...) Bilder ... . Noch/Schon ... Anrisse. Verschleiß ... erkennbar.
+... 6,8 Nm -&gt; nachverspannt auf ... Nm bei TA ... °C, TP ... °C ;  (ca. ... Nm Verlust über ...) Bilder ... . Noch/Schon ... Anrisse. Verschleiß ... erkennbar.
+... 6,8 Nm -&gt; nachverspannt auf ... Nm bei TA ... °C, TP ... °C ;  (ca. ... Nm Verlust über ...) Bilder ... . Noch/Schon ... Anrisse. Verschleiß ... erkennbar.
+... 6,8 Nm -&gt; nachverspannt auf ... Nm bei TA ... °C, TP ... °C ;  (ca. ... Nm Verlust über ...) Bilder ... . Noch/Schon ... Anrisse. Verschleiß ... erkennbar.</t>
   </si>
 </sst>
 </file>
@@ -2014,32 +2023,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C3A9485-4D50-0041-9D5B-E8D35C0F1538}">
   <dimension ref="A1:U103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4.625" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.875" customWidth="1"/>
     <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="5.33203125" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="157" customWidth="1"/>
+    <col min="7" max="7" width="5.375" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="157" customWidth="1"/>
     <col min="9" max="9" width="5.5" customWidth="1"/>
-    <col min="10" max="10" width="26.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="8.1640625" customWidth="1"/>
-    <col min="13" max="13" width="19.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.1640625" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="4.1640625" customWidth="1"/>
-    <col min="17" max="17" width="10.33203125" customWidth="1"/>
-    <col min="18" max="18" width="9.1640625" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="11" max="11" width="8.625" customWidth="1"/>
+    <col min="12" max="12" width="8.125" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
+    <col min="14" max="14" width="19.125" customWidth="1"/>
+    <col min="15" max="15" width="12.875" customWidth="1"/>
+    <col min="16" max="16" width="4.125" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="18" max="18" width="9.125" customWidth="1"/>
     <col min="19" max="19" width="13.5" customWidth="1"/>
     <col min="20" max="20" width="148" style="158" customWidth="1"/>
     <col min="21" max="21" width="195.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2102,7 +2111,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>20</v>
       </c>
@@ -2145,7 +2154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>25</v>
       </c>
@@ -2185,7 +2194,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>26</v>
       </c>
@@ -2225,7 +2234,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>28</v>
       </c>
@@ -2265,7 +2274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:21" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>31</v>
       </c>
@@ -2306,7 +2315,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" s="5" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
@@ -2362,7 +2371,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:21" s="14" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:21" s="14" customFormat="1" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>36</v>
       </c>
@@ -2418,7 +2427,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:21" s="22" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:21" s="22" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>38</v>
       </c>
@@ -2475,7 +2484,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:21" s="29" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" s="29" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>42</v>
       </c>
@@ -2535,7 +2544,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" s="36" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>45</v>
       </c>
@@ -2595,7 +2604,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:21" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" s="29" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>48</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:21" s="36" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" s="36" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>51</v>
       </c>
@@ -2715,7 +2724,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:21" s="36" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" s="36" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>54</v>
       </c>
@@ -2775,7 +2784,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:21" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>57</v>
       </c>
@@ -2835,7 +2844,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:21" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" s="36" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
         <v>61</v>
       </c>
@@ -2895,7 +2904,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:20" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
         <v>65</v>
       </c>
@@ -2955,7 +2964,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
         <v>68</v>
       </c>
@@ -3015,7 +3024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:20" s="36" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
         <v>71</v>
       </c>
@@ -3075,7 +3084,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="48" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" s="48" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="46" t="s">
         <v>74</v>
       </c>
@@ -3135,7 +3144,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:20" s="53" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>78</v>
       </c>
@@ -3195,7 +3204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>81</v>
       </c>
@@ -3255,7 +3264,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>84</v>
       </c>
@@ -3315,7 +3324,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="64" t="s">
         <v>88</v>
       </c>
@@ -3375,7 +3384,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="74" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="70" t="s">
         <v>92</v>
       </c>
@@ -3435,7 +3444,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="82" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" s="82" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="78" t="s">
         <v>96</v>
       </c>
@@ -3495,7 +3504,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="85" t="s">
         <v>100</v>
       </c>
@@ -3555,7 +3564,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="85" t="s">
         <v>103</v>
       </c>
@@ -3615,7 +3624,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="91" t="s">
         <v>106</v>
       </c>
@@ -3675,7 +3684,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:20" s="93" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="91" t="s">
         <v>110</v>
       </c>
@@ -3735,7 +3744,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:20" s="74" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" s="74" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="70" t="s">
         <v>115</v>
       </c>
@@ -3795,7 +3804,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:20" s="101" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:20" s="101" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="99" t="s">
         <v>119</v>
       </c>
@@ -3855,7 +3864,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:20" s="108" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:20" s="108" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="106" t="s">
         <v>122</v>
       </c>
@@ -3915,7 +3924,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="112" t="s">
         <v>125</v>
       </c>
@@ -3975,7 +3984,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="35" spans="1:20" s="121" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:20" s="121" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="118" t="s">
         <v>130</v>
       </c>
@@ -4035,7 +4044,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:20" s="114" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:20" s="114" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="112" t="s">
         <v>133</v>
       </c>
@@ -4095,7 +4104,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="37" spans="1:20" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:20" s="30" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="85" t="s">
         <v>140</v>
       </c>
@@ -4155,7 +4164,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="1:20" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:20" s="30" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="85" t="s">
         <v>143</v>
       </c>
@@ -4215,7 +4224,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="39" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:20" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="85" t="s">
         <v>147</v>
       </c>
@@ -4275,7 +4284,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="64" t="s">
         <v>150</v>
       </c>
@@ -4335,7 +4344,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="41" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="64" t="s">
         <v>154</v>
       </c>
@@ -4395,7 +4404,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="42" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:20" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="40" t="s">
         <v>157</v>
       </c>
@@ -4456,7 +4465,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:20" s="82" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" s="82" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="78" t="s">
         <v>160</v>
       </c>
@@ -4516,7 +4525,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:20" s="134" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:20" s="134" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="40" t="s">
         <v>163</v>
       </c>
@@ -4569,7 +4578,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="45" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:20" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="36" t="s">
         <v>165</v>
       </c>
@@ -4605,7 +4614,7 @@
       </c>
       <c r="T45" s="38"/>
     </row>
-    <row r="46" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:20" s="114" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="114" t="s">
         <v>166</v>
       </c>
@@ -4642,7 +4651,7 @@
       </c>
       <c r="T46" s="116"/>
     </row>
-    <row r="47" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="135" t="s">
         <v>167</v>
       </c>
@@ -4666,7 +4675,7 @@
       </c>
       <c r="T47" s="139"/>
     </row>
-    <row r="48" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="135" t="s">
         <v>168</v>
       </c>
@@ -4690,7 +4699,7 @@
       </c>
       <c r="T48" s="139"/>
     </row>
-    <row r="49" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="135" t="s">
         <v>169</v>
       </c>
@@ -4715,7 +4724,7 @@
       </c>
       <c r="T49" s="139"/>
     </row>
-    <row r="50" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:20" s="135" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="135" t="s">
         <v>170</v>
       </c>
@@ -4741,7 +4750,7 @@
       <c r="R50" s="142"/>
       <c r="T50" s="139"/>
     </row>
-    <row r="51" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="135" t="s">
         <v>171</v>
       </c>
@@ -4795,7 +4804,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="52" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="135" t="s">
         <v>176</v>
       </c>
@@ -4849,7 +4858,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="53" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="135" t="s">
         <v>178</v>
       </c>
@@ -4903,7 +4912,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="54" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="135" t="s">
         <v>180</v>
       </c>
@@ -4958,7 +4967,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="55" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="135" t="s">
         <v>184</v>
       </c>
@@ -4986,7 +4995,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="135" t="s">
         <v>185</v>
       </c>
@@ -5010,7 +5019,7 @@
       </c>
       <c r="T56" s="139"/>
     </row>
-    <row r="57" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="135" t="s">
         <v>186</v>
       </c>
@@ -5034,7 +5043,7 @@
       </c>
       <c r="T57" s="139"/>
     </row>
-    <row r="58" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="135" t="s">
         <v>187</v>
       </c>
@@ -5058,7 +5067,7 @@
       </c>
       <c r="T58" s="139"/>
     </row>
-    <row r="59" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="135" t="s">
         <v>188</v>
       </c>
@@ -5083,7 +5092,7 @@
       </c>
       <c r="T59" s="139"/>
     </row>
-    <row r="60" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="135" t="s">
         <v>189</v>
       </c>
@@ -5109,7 +5118,7 @@
       <c r="R60" s="142"/>
       <c r="T60" s="139"/>
     </row>
-    <row r="61" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="135" t="s">
         <v>190</v>
       </c>
@@ -5133,7 +5142,7 @@
       </c>
       <c r="T61" s="139"/>
     </row>
-    <row r="62" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="135" t="s">
         <v>191</v>
       </c>
@@ -5157,7 +5166,7 @@
       </c>
       <c r="T62" s="139"/>
     </row>
-    <row r="63" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="135" t="s">
         <v>192</v>
       </c>
@@ -5181,7 +5190,7 @@
       </c>
       <c r="T63" s="139"/>
     </row>
-    <row r="64" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="135" t="s">
         <v>184</v>
       </c>
@@ -5236,7 +5245,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="65" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="135" t="s">
         <v>185</v>
       </c>
@@ -5293,7 +5302,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="135" t="s">
         <v>186</v>
       </c>
@@ -5348,7 +5357,7 @@
       </c>
       <c r="T66" s="139"/>
     </row>
-    <row r="67" spans="1:20" s="143" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:20" s="143" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="135" t="s">
         <v>187</v>
       </c>
@@ -5407,7 +5416,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="135" t="s">
         <v>188</v>
       </c>
@@ -5464,7 +5473,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:20" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="135" t="s">
         <v>189</v>
       </c>
@@ -5523,7 +5532,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="135" t="s">
         <v>190</v>
       </c>
@@ -5582,7 +5591,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="144" t="s">
         <v>191</v>
       </c>
@@ -5641,7 +5650,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="72" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="135" t="s">
         <v>188</v>
       </c>
@@ -5674,7 +5683,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="73" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="135" t="s">
         <v>189</v>
       </c>
@@ -5705,7 +5714,7 @@
       </c>
       <c r="T73" s="160"/>
     </row>
-    <row r="74" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="135" t="s">
         <v>190</v>
       </c>
@@ -5736,7 +5745,7 @@
       </c>
       <c r="T74" s="161"/>
     </row>
-    <row r="75" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="135" t="s">
         <v>191</v>
       </c>
@@ -5770,7 +5779,7 @@
       </c>
       <c r="T75" s="139"/>
     </row>
-    <row r="76" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:20" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="135" t="s">
         <v>192</v>
       </c>
@@ -5821,7 +5830,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="148" t="s">
         <v>210</v>
       </c>
@@ -5869,7 +5878,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="78" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="149">
         <v>46252</v>
       </c>
@@ -5914,7 +5923,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="79" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="149">
         <v>46252</v>
       </c>
@@ -5956,7 +5965,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="80" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:20" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="149">
         <v>46252</v>
       </c>
@@ -5998,7 +6007,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="81" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="149">
         <v>46253</v>
       </c>
@@ -6043,7 +6052,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="149">
         <v>46253</v>
       </c>
@@ -6088,7 +6097,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="83" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:21" s="148" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="149">
         <v>46255</v>
       </c>
@@ -6120,7 +6129,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="84" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="135" t="s">
         <v>230</v>
       </c>
@@ -6168,7 +6177,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:21" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="135" t="s">
         <v>232</v>
       </c>
@@ -6219,7 +6228,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="86" spans="1:21" s="148" customFormat="1" ht="32" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:21" s="148" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="148" t="s">
         <v>234</v>
       </c>
@@ -6267,7 +6276,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="87" spans="1:21" s="143" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:21" s="143" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="153" t="s">
         <v>238</v>
       </c>
@@ -6319,7 +6328,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="88" spans="1:21" s="148" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:21" s="148" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A88" s="148" t="s">
         <v>240</v>
       </c>
@@ -6373,7 +6382,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:21" s="148" customFormat="1" ht="240" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:21" s="148" customFormat="1" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A89" s="148" t="s">
         <v>245</v>
       </c>
@@ -6430,7 +6439,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:21" s="148" customFormat="1" ht="48" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:21" s="148" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A90" s="148" t="s">
         <v>251</v>
       </c>
@@ -6487,7 +6496,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="91" spans="1:21" s="148" customFormat="1" ht="240" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:21" s="148" customFormat="1" ht="236.25" x14ac:dyDescent="0.25">
       <c r="A91" s="148" t="s">
         <v>254</v>
       </c>
@@ -6544,7 +6553,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:21" s="148" customFormat="1" ht="160" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:21" s="148" customFormat="1" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A92" s="148" t="s">
         <v>257</v>
       </c>
@@ -6601,7 +6610,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="93" spans="1:21" s="148" customFormat="1" ht="128" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:21" s="148" customFormat="1" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A93" s="148" t="s">
         <v>262</v>
       </c>
@@ -6655,7 +6664,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="94" spans="1:21" s="148" customFormat="1" ht="256" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:21" s="148" customFormat="1" ht="252" x14ac:dyDescent="0.25">
       <c r="A94" s="148" t="s">
         <v>267</v>
       </c>
@@ -6712,7 +6721,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="95" spans="1:21" s="148" customFormat="1" ht="272" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:21" s="148" customFormat="1" ht="283.5" x14ac:dyDescent="0.25">
       <c r="A95" s="148" t="s">
         <v>271</v>
       </c>
@@ -6765,12 +6774,52 @@
       </c>
       <c r="U95" s="156"/>
     </row>
-    <row r="97" spans="20:20" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:21" s="148" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="A96" s="148" t="s">
+        <v>278</v>
+      </c>
+      <c r="B96" s="149"/>
+      <c r="C96" s="148" t="s">
+        <v>172</v>
+      </c>
+      <c r="D96" s="148" t="s">
+        <v>211</v>
+      </c>
+      <c r="E96" s="148">
+        <v>95919</v>
+      </c>
+      <c r="F96" s="148">
+        <v>97361</v>
+      </c>
+      <c r="G96" s="148">
+        <v>75</v>
+      </c>
+      <c r="H96" s="150">
+        <v>80</v>
+      </c>
+      <c r="J96" s="156"/>
+      <c r="K96" s="148">
+        <v>7.8</v>
+      </c>
+      <c r="M96" s="156"/>
+      <c r="Q96" s="148">
+        <f>K96*(52/51)</f>
+        <v>7.9529411764705875</v>
+      </c>
+      <c r="R96" s="148">
+        <v>3058</v>
+      </c>
+      <c r="T96" s="152" t="s">
+        <v>279</v>
+      </c>
+      <c r="U96" s="156"/>
+    </row>
+    <row r="97" spans="20:20" x14ac:dyDescent="0.25">
       <c r="T97" s="158" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="103" spans="20:20" x14ac:dyDescent="0.4">
+    <row r="103" spans="20:20" x14ac:dyDescent="0.25">
       <c r="T103" s="158" t="s">
         <v>216</v>
       </c>
